--- a/NECP Scenario/Results/Regional Results/SERIFOS_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/SERIFOS_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.275895206721135E-08</v>
+        <v>4.798693281607373E-08</v>
       </c>
       <c r="C3">
-        <v>3.298332857416024E-08</v>
+        <v>4.824454574315944E-08</v>
       </c>
       <c r="D3">
-        <v>0.2227645566137401</v>
+        <v>0.2596093410160572</v>
       </c>
       <c r="E3">
-        <v>0.222764556777219</v>
+        <v>0.2596093415123127</v>
       </c>
       <c r="F3">
-        <v>0.2227645243192111</v>
+        <v>0.2596092950201301</v>
       </c>
       <c r="G3">
-        <v>0.2270102167423897</v>
+        <v>0.2661854161941102</v>
       </c>
       <c r="H3">
-        <v>0.2342295710320616</v>
+        <v>0.2754565433448823</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4000000000065802</v>
+        <v>0.4000000000069811</v>
       </c>
       <c r="C13">
-        <v>0.4000000000086229</v>
+        <v>0.4000000000099812</v>
       </c>
       <c r="D13">
-        <v>0.4000000000125723</v>
+        <v>0.4000000000158414</v>
       </c>
       <c r="E13">
-        <v>0.4000000000233011</v>
+        <v>0.4000000000287956</v>
       </c>
       <c r="F13">
-        <v>0.4000000000404156</v>
+        <v>0.4000000000493239</v>
       </c>
       <c r="G13">
-        <v>0.4000000000744053</v>
+        <v>0.4000000000946285</v>
       </c>
       <c r="H13">
-        <v>0.4000000004233661</v>
+        <v>0.400000000504695</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.026340294711253</v>
+        <v>0.0303925671983316</v>
       </c>
       <c r="E27">
-        <v>0.0360112297561776</v>
+        <v>0.0360112299415389</v>
       </c>
       <c r="F27">
-        <v>0.0360112304752115</v>
+        <v>0.0360112304199283</v>
       </c>
       <c r="G27">
-        <v>0.036011230733253</v>
+        <v>0.0360112306674475</v>
       </c>
       <c r="H27">
-        <v>0.0360112308816827</v>
+        <v>0.0360112308513581</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0.0013786502975611</v>
+        <v>0.0013786631354274</v>
       </c>
       <c r="E29">
-        <v>0.0017248418106951</v>
+        <v>0.0020022267210348</v>
       </c>
       <c r="F29">
-        <v>0.0020975834602924</v>
+        <v>0.0020975835166723</v>
       </c>
       <c r="G29">
-        <v>0.002097583813396</v>
+        <v>0.0020975837785407</v>
       </c>
       <c r="H29">
-        <v>0.0020975839210226</v>
+        <v>0.002097583904131</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.253399153643558</v>
+        <v>0.2441522382493572</v>
       </c>
       <c r="E33">
-        <v>0.2607446478314403</v>
+        <v>0.2599455140934114</v>
       </c>
       <c r="F33">
-        <v>0.266755224155671</v>
+        <v>0.267749329925224</v>
       </c>
       <c r="G33">
-        <v>0.2667552251815883</v>
+        <v>0.2677493319016866</v>
       </c>
       <c r="H33">
-        <v>0.2667552274930075</v>
+        <v>0.2677493347377839</v>
       </c>
     </row>
     <row r="34" spans="1:8">
